--- a/public/assets/BOs/Isis.xlsx
+++ b/public/assets/BOs/Isis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\doc\coding\DoD\DeitiesOfDeath\public\assets\BOs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris\OneDrive\Github\Deities of Death\public\assets\BOs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97C94FC6-F76C-41B7-B89B-07AF116D74B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD46017-67B9-44DF-BA08-3CAF36BE41C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil5" sheetId="6" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="118">
   <si>
     <t>Archaic</t>
   </si>
@@ -1235,17 +1235,27 @@
   </si>
   <si>
     <t>Water - Medit BO - By BacHi</t>
+  </si>
+  <si>
+    <t>4/0/5/1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1462,70 +1472,68 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{8331A63F-6C66-48DA-9DF7-BB253F542590}"/>
   </cellStyles>
@@ -1741,25 +1749,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37E98EEE-A8F8-4B5F-97DB-3264567D6200}">
   <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+      <c r="A1" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-    </row>
-    <row r="3" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+    </row>
+    <row r="3" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
@@ -1767,7 +1775,7 @@
       <c r="C3" s="14"/>
       <c r="D3" s="14"/>
     </row>
-    <row r="4" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>70</v>
       </c>
@@ -1777,7 +1785,7 @@
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
     </row>
-    <row r="5" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>72</v>
       </c>
@@ -1787,7 +1795,7 @@
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
     </row>
-    <row r="6" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>74</v>
       </c>
@@ -1797,7 +1805,7 @@
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
     </row>
-    <row r="7" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>76</v>
       </c>
@@ -1807,7 +1815,7 @@
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
     </row>
-    <row r="8" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A8" s="14"/>
       <c r="B8" s="14" t="s">
         <v>77</v>
@@ -1815,27 +1823,27 @@
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
     </row>
-    <row r="9" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A9" s="14"/>
       <c r="B9" s="14"/>
       <c r="C9" s="9"/>
       <c r="D9" s="14"/>
     </row>
-    <row r="10" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A10" s="14"/>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+    <row r="11" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-    </row>
-    <row r="12" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+    </row>
+    <row r="12" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>93</v>
       </c>
@@ -1845,7 +1853,7 @@
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
     </row>
-    <row r="13" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A13" s="15"/>
       <c r="B13" s="14" t="s">
         <v>80</v>
@@ -1853,21 +1861,21 @@
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
     </row>
-    <row r="14" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A14" s="14"/>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+    <row r="15" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-    </row>
-    <row r="16" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+    </row>
+    <row r="16" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16" s="14" t="s">
         <v>94</v>
@@ -1875,7 +1883,7 @@
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
     </row>
-    <row r="17" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A17" s="14"/>
       <c r="B17" s="11" t="s">
         <v>82</v>
@@ -1883,7 +1891,7 @@
       <c r="C17" s="11"/>
       <c r="D17" s="12"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="8"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -1903,25 +1911,25 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CB30BBB-0977-448C-803B-BA7A3D9A0DD7}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+      <c r="A1" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-    </row>
-    <row r="3" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+    </row>
+    <row r="3" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
@@ -1929,7 +1937,7 @@
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
     </row>
-    <row r="4" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>70</v>
       </c>
@@ -1939,9 +1947,9 @@
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
     </row>
-    <row r="5" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
-        <v>72</v>
+    <row r="5" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="A5" s="32" t="s">
+        <v>117</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>73</v>
@@ -1949,7 +1957,7 @@
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
     </row>
-    <row r="6" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>74</v>
       </c>
@@ -1959,7 +1967,7 @@
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
     </row>
-    <row r="7" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>83</v>
       </c>
@@ -1969,33 +1977,33 @@
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
     </row>
-    <row r="8" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A8" s="10"/>
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
     </row>
-    <row r="9" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A9" s="10"/>
       <c r="B9" s="10"/>
       <c r="C9" s="9"/>
       <c r="D9" s="10"/>
     </row>
-    <row r="10" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A10" s="10"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
     </row>
-    <row r="11" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+    <row r="11" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-    </row>
-    <row r="12" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+    </row>
+    <row r="12" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>85</v>
       </c>
@@ -2005,7 +2013,7 @@
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
     </row>
-    <row r="13" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A13" s="13"/>
       <c r="B13" s="10" t="s">
         <v>80</v>
@@ -2013,7 +2021,7 @@
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
     </row>
-    <row r="14" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
       <c r="B14" s="11" t="s">
         <v>87</v>
@@ -2021,15 +2029,15 @@
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
     </row>
-    <row r="15" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+    <row r="15" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-    </row>
-    <row r="16" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+    </row>
+    <row r="16" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A16" s="13"/>
       <c r="B16" s="10" t="s">
         <v>88</v>
@@ -2037,7 +2045,7 @@
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
     </row>
-    <row r="17" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A17" s="10"/>
       <c r="B17" s="11" t="s">
         <v>89</v>
@@ -2059,151 +2067,143 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90D76AB9-4ADE-4F71-9B12-F382E3DA9BF5}">
   <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:4" ht="19" x14ac:dyDescent="0.4">
+      <c r="A1" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-    </row>
-    <row r="2" spans="1:4" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+    </row>
+    <row r="2" spans="1:4" ht="20" x14ac:dyDescent="0.4">
+      <c r="A2" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-    </row>
-    <row r="3" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+    </row>
+    <row r="3" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="23"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="23"/>
-    </row>
-    <row r="4" spans="1:4" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A4" s="28" t="s">
+      <c r="C3" s="17"/>
+    </row>
+    <row r="4" spans="1:4" ht="88" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="C4" s="25"/>
-      <c r="D4" s="29" t="s">
+      <c r="C4" s="17"/>
+      <c r="D4" s="20" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="28" t="s">
+    <row r="5" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="23" t="s">
+      <c r="C5" s="17"/>
+      <c r="D5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="114.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="28" t="s">
+    <row r="6" spans="1:4" ht="113" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="27" t="s">
+      <c r="C6" s="17"/>
+      <c r="D6" s="19" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="293.25" x14ac:dyDescent="0.2">
-      <c r="A7" s="28" t="s">
+    <row r="7" spans="1:4" ht="288" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C7" s="25"/>
-      <c r="D7" s="29" t="s">
+      <c r="C7" s="17"/>
+      <c r="D7" s="20" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="26"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-    </row>
-    <row r="9" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="34" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+    </row>
+    <row r="9" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-    </row>
-    <row r="10" spans="1:4" ht="409.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="32" t="s">
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+    </row>
+    <row r="10" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="29" t="s">
+      <c r="C10" s="17"/>
+      <c r="D10" s="20" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="34" t="s">
+    <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="31" t="s">
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="22" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="28" t="s">
+    <row r="13" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="31" t="s">
+      <c r="C13" s="17"/>
+      <c r="D13" s="22" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="25"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="23"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="23"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="23"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="23"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="23"/>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="17"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C16" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2222,31 +2222,31 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:D20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.28515625" customWidth="1"/>
-    <col min="2" max="2" width="63.7109375" customWidth="1"/>
-    <col min="3" max="3" width="62.5703125" customWidth="1"/>
+    <col min="1" max="1" width="32.26953125" customWidth="1"/>
+    <col min="2" max="2" width="63.7265625" customWidth="1"/>
+    <col min="3" max="3" width="62.54296875" customWidth="1"/>
     <col min="4" max="4" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-    </row>
-    <row r="3" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+    </row>
+    <row r="3" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -2254,7 +2254,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -2278,7 +2278,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -2302,7 +2302,7 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -2312,7 +2312,7 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -2322,7 +2322,7 @@
       <c r="C9" s="2"/>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -2334,15 +2334,15 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+    <row r="11" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-    </row>
-    <row r="12" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+    </row>
+    <row r="12" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
@@ -2350,7 +2350,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
         <v>22</v>
@@ -2358,7 +2358,7 @@
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
     </row>
-    <row r="14" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
@@ -2370,15 +2370,15 @@
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="21" t="s">
+    <row r="15" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-    </row>
-    <row r="16" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+    </row>
+    <row r="16" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>1</v>
       </c>
@@ -2386,7 +2386,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>28</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>31</v>
       </c>
@@ -2410,7 +2410,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>67</v>
       </c>
@@ -2418,7 +2418,7 @@
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
     </row>
-    <row r="20" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -2441,28 +2441,28 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4DBAFE0-52F5-4DF4-A814-454F2AD29450}">
   <dimension ref="A1:D27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="72.28515625" customWidth="1"/>
+    <col min="1" max="1" width="72.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+      <c r="A1" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+    </row>
+    <row r="2" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-    </row>
-    <row r="3" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+    </row>
+    <row r="3" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -2470,7 +2470,7 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -2494,7 +2494,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -2518,7 +2518,7 @@
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -2528,7 +2528,7 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>35</v>
       </c>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>38</v>
       </c>
@@ -2562,7 +2562,7 @@
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
     </row>
-    <row r="12" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>40</v>
       </c>
@@ -2572,7 +2572,7 @@
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
     </row>
-    <row r="13" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>42</v>
       </c>
@@ -2584,15 +2584,15 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
+    <row r="14" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+    </row>
+    <row r="15" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>46</v>
       </c>
@@ -2604,15 +2604,15 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
+    <row r="16" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-    </row>
-    <row r="17" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+    </row>
+    <row r="17" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>1</v>
       </c>
@@ -2620,7 +2620,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="2" t="s">
         <v>50</v>
@@ -2628,7 +2628,7 @@
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
     </row>
-    <row r="19" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>51</v>
       </c>
@@ -2638,7 +2638,7 @@
       <c r="C19" s="1"/>
       <c r="D19" s="4"/>
     </row>
-    <row r="20" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>52</v>
       </c>
@@ -2648,7 +2648,7 @@
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
     </row>
-    <row r="21" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>54</v>
       </c>
@@ -2658,15 +2658,15 @@
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
     </row>
-    <row r="22" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="21" t="s">
+    <row r="22" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-    </row>
-    <row r="23" spans="1:4" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+    </row>
+    <row r="23" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>1</v>
       </c>
@@ -2674,7 +2674,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>58</v>
       </c>
@@ -2688,7 +2688,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="14" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>62</v>
       </c>
@@ -2699,15 +2699,15 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="21" t="s">
+    <row r="26" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>66</v>
       </c>
